--- a/reddit_data_export.xlsx
+++ b/reddit_data_export.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reddit Posts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reddit Comments" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q&amp;A Pairs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Reddit Posts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reddit Comments" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Q&amp;A Pairs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reddit Posts'!$A$1:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reddit Comments'!$A$1:$I$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Q&amp;A Pairs'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reddit Posts'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reddit Comments'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Q&amp;A Pairs'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,18 +441,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,39 +473,39 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Url</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Created Utc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Num Comments</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Url</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Created Utc</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Inserted At</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_testpost1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -515,36 +515,40 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Death of Yves Sakila, a Congolese man renews scrutiny of race relations in Ireland</t>
+          <t>SQLite Migration Test Post</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mean_Yak5873</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+          <t>This is a test post to verify database migrations and relationships.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>test_author</t>
+        </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/news/comments/1ugnqsp/death_of_yves_sakila_a_congolese_man_renews/</t>
+          <t>https://reddit.com/r/news/testpost1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 00:19:37</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>2026-07-18T00:34:13.895131</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz9bsm</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -554,36 +558,40 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Power outages, fuel bans and no summer camps: Crimea placed under state of emergency as Ukraine steps up pressure on Putin</t>
+          <t>US strikes bridges in Iran, which targets a water desalination plant in Kuwait</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>DQ-Supervisor</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
+          <t>&amp;#32; submitted by &amp;#32;  /u/NicolasCageFan492   [link] &amp;#32; [comments]</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>NicolasCageFan492</t>
+        </is>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/news/comments/1ugm42w/power_outages_fuel_bans_and_no_summer_camps/</t>
+          <t>https://www.reddit.com/r/news/comments/1uz9bsm/us_strikes_bridges_in_iran_which_targets_a_water/</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 23:09:36</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:17:34+00:00</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -593,73 +601,124 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Over 100 dogs found dead, many with bullet holes at Northern California rescue, authorities say</t>
+          <t>Rapper Desiigner arrested again in Horry County, accused of chasing victim with hammer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>licecrispies</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
+          <t>&amp;#32; submitted by &amp;#32;  /u/btg7471   [link] &amp;#32; [comments]</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>btg7471</t>
+        </is>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/news/comments/1ugkucg/over_100_dogs_found_dead_many_with_bullet_holes/</t>
+          <t>https://www.reddit.com/r/news/comments/1uz893y/rapper_desiigner_arrested_again_in_horry_county/</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 22:16:39</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:38:22+00:00</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>t3_vwi6jx</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Pasta Peperoni and Ricotta cheese (how to make Peperoni sauce very very creamy). Hello I'm Vito from Italy:-) and this is on of my fav recipe. Full video procedure and recipe in the comment. Try to cook it and let me know the result. Ciao ciao :-)</t>
+          <t>Fairlife pauses US production after cyberattack breached milk brand's systems</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cooking_Vito_e_Daisy</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
+          <t>&amp;#32; submitted by &amp;#32;  /u/AudibleNod   [link] &amp;#32; [comments]</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>AudibleNod</t>
+        </is>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/pasta/comments/vwi6jx/pasta_peperoni_and_ricotta_cheese_how_to_make/</t>
+          <t>https://www.reddit.com/r/news/comments/1uz7n6y/fairlife_pauses_us_production_after_cyberattack/</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2022-07-11 13:15:17</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:16:53+00:00</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>t3_1uz7dga</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Flock cameras misused - law enforcement fired</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>&amp;#32; submitted by &amp;#32;  /u/lurkynic   [link] &amp;#32; [comments]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>lurkynic</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/news/comments/1uz7dga/flock_cameras_misused_law_enforcement_fired/</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -670,18 +729,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,36 +783,31 @@
           <t>Created Utc</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Inserted At</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>t1_ou3tz0b</t>
+          <t>t1_oy55d5i</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Short_Ad_5006</t>
+          <t>Double-O-stoopid</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>race relations  The guy kneeling on his back the entire incident was black ffs. The guardian is well known for hating Ireland and this is just another example</t>
+          <t>See I think it&amp;#39;s at least 4 more. He has family in law enforcement (they all do). We, as a people, get to roll the dice and give all of them the benefit of the doubt. Wouldn&amp;#39;t be &amp;quot;fair&amp;quot; otherwise, yeah?</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -765,35 +818,34 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 10:56:59</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:21:15+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>t1_ou49dat</t>
+          <t>t1_oy5b1yw</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Dull_Consequence7192</t>
+          <t>New-Ad-363</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>It&amp;#39;s a rag. I love how they beg for money on their website. I can&amp;#39;t wait until they close.</t>
+          <t>Water usage</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -804,35 +856,34 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 12:40:06</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:45:36+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>t1_ou3enl4</t>
+          <t>t1_oy561vm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Complex_Spare_7278</t>
+          <t>torque1912</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>This man died not because of racism, but because the government refuses to address crime by keep a profesionally trained police force fully staffed/ equipped and they refuse to address the problem that petty crimes go unpunished . Private businesses are then forced to pay for private security, hiring untrained and inexperienced people while the guards standards are also deteriorating.</t>
+          <t>For real. The fact that they have an AI audit program that corroborates the complaints makes me say “why not run that program continuously so that when they’re being used illegally, a message gets sent to the town hall (or another sort of agency that has no affiliation with the PD so there is never any conflict of interest) and the wrongful use is made public immediately. I don’t agree with the cameras in general AT ALL, but if they’re gonna force them on certain towns for “public safety” use the said auditing program simultaneously and prove it’s strictly for “public safety”. Cuz like your original comment, this one incident is offset by 1000 that haven’t been caught and/or reported. And the whole “how they used the cameras illegally has not been disclosed” bullshit. Sure….. It seems most the incidents I’ve heard of, they use the cameras to stalk exes or use it to bust the balls of people they don’t like. “Here’s 13 speeding tickets/driving infractions and 25 parking tickets from your drive home from work yesterday”</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -843,35 +894,34 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 08:49:42</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:24:10+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>t1_ou1ev9q</t>
+          <t>t1_oy52yrs</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7dga</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Mean_Yak5873</t>
+          <t>smkmn13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>In the released footage it shows that Yves was held down by 6 security guards where he was pinned face down. They put a bag over his head and one of the security guards was recorded pressing his knee on Yves’s neck.</t>
+          <t>Every time a story like this comes out, remember...this is just one we know about...</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -882,35 +932,34 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 00:33:54</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:11:07+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>t1_ou3ucs8</t>
+          <t>t1_oy5i8i0</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Short_Ad_5006</t>
+          <t>Zestyclose-Novel1157</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Why dont you mention that some of the security guards were black? Its almost like youre a race baiting moron</t>
+          <t>Pft I wish it was 4 a gallon. I’ve never lived somewhere as expensive for groceries as I do now. It’s $5.50 a gallon for plain milk, not even fancy stuff.</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -921,35 +970,34 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 10:59:53</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:16:53+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>t1_ou1iugj</t>
+          <t>t1_oy5d562</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Contren</t>
+          <t>MountainFriend7473</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Seems they&amp;#39;ve been training with US cops...</t>
+          <t>5 for lactose free 2% where I live</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -960,35 +1008,34 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 00:56:23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:54:37+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>t1_ou1id5d</t>
+          <t>t1_oy5bcxk</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>samsaruhhh</t>
+          <t>klaatu7764</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>So an execution in the street</t>
+          <t>Lucky moo!</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -999,35 +1046,34 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 00:53:40</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:46:53+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>t1_ou2vtr7</t>
+          <t>t1_oy5a7vc</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SoloWingPixy88</t>
+          <t>DocHolidayiN</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>No video of a bag over his head?</t>
+          <t>Dairy country.</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1038,35 +1084,34 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 06:12:37</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:42:00+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>t1_ou345m2</t>
+          <t>t1_oy56fll</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Mean_Yak5873</t>
+          <t>klaatu7764</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>In footage captured by a bystander, two of the security guards are seen holding a black sack over his head.</t>
+          <t>Only $4?</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1077,35 +1122,34 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 07:19:56</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:25:47+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>t1_ou3ts1u</t>
+          <t>t1_oy55gun</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugnqsp</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>SoloWingPixy88</t>
+          <t>Subarctic_Monkey</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>No that was a spit hoodvto stop sakila from spitting on people after he robbed the shop and hospitalised an 86 year old man as he tried to escape.  I&amp;#39;m not defending the security guards, they&amp;#39;re not trained in restraining a person and they shouldn&amp;#39;t of been on top of him. I wouldn&amp;#39;t be surprised if manslaughter charges are brought up. Just educating you on what exactly happened from an objective view.</t>
+          <t>Especially Fairlife.</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1116,35 +1160,34 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 10:55:30</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:21:41+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>t1_ou11mg7</t>
+          <t>t1_oy593ey</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Full-Hold-9447</t>
+          <t>AKStafford</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Slava Ukraine. Keep the pressure on.</t>
+          <t>I&amp;#39;m paying $5 a gallon now for regular store brand milk.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1155,35 +1198,34 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 23:20:06</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:37:11+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>t1_ou12j8y</t>
+          <t>t1_oy5h4va</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>RunDownTheHighway</t>
+          <t>run-on_sentience</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>If they hadnt stolen Crimea in the first place, vlad wouldnt have to worry about lack of summer camps...</t>
+          <t>At the discount grocery store I go to, it&amp;#39;s $4.89 for a 52 oz container. Other stores it&amp;#39;s $5.50. So it&amp;#39;s actually even more expensive. $12--$13.50 a gallon.</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1194,35 +1236,34 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 23:25:00</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:12:02+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>t1_ou11xrd</t>
+          <t>t1_oy56gn9</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Fallouttgrrl</t>
+          <t>Steez_And_Rice</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>&amp;quot;power outage, fuel bans, and no summer camp&amp;quot; is the wildest &amp;quot;arson, murder, and jaywalking&amp;quot; I&amp;#39;ve seen</t>
+          <t>Fair life is like $10 a gallon</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1233,35 +1274,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 23:21:47</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:25:55+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>t1_ou2ic5w</t>
+          <t>t1_oy55dqa</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz7n6y</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>steathrazor</t>
+          <t>DocHolidayiN</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Truth, one of these isn&amp;#39;t like the others</t>
+          <t>Milk (like everything else has increased) is $4 a gallon so I imagine this will be used to raise prices.</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1272,35 +1312,34 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 04:32:52</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:21:19+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>t1_ou42hvn</t>
+          <t>t1_oy5dj5e</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hedge_the_Hog_HtH</t>
+          <t>UBC145</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>&amp;quot;Артек(Artek)&amp;quot; was THE summer camp for Soviet Union. Children went there basically as a reward for winning some state/international competition(or being born in elite family), so it still has the image of prestige, despite not being prestigeous anymore. That&amp;#39;s why the news of its closure is very noticable.</t>
+          <t>Who amongst us hasn’t chased a fellow man with a hammer in the heat of passion?</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1311,35 +1350,34 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 11:56:59</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:56:18+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>t1_ou4lgvs</t>
+          <t>t1_oy5dz1w</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>rockmasterflex</t>
+          <t>ghidfg</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>won&amp;#39;t anyone think of the poor summer camps.</t>
+          <t>New English was amazing</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1350,35 +1388,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 13:47:13</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:58:14+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>t1_ou13zbh</t>
+          <t>t1_oy5blh9</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>sojuz151</t>
+          <t>GhostGrayZ51</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>I still can&amp;#39;t understand why Biden&amp;#39;s administration was drip feeding Ukraine are refusing to support long range strikes.</t>
+          <t>Timmy, Timmy, Timmy Turner, he been lookin for a burner.  Tequila and hot water, show me the the sun and I farted.  Or something like that...</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1389,35 +1426,34 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 23:32:48</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:47:54+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>t1_ou1p9vd</t>
+          <t>t1_oy5ffg9</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Hellstorm901</t>
+          <t>RPDRNick</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Everyone thought Russia was stronger than it was and that Putin would escalate it he was pushed We now know the Russian military is beyond a joke, we overestimated the abilities of their troops and equipment and that when Putin is stood up to he ended up backing down rather then acting on his threats</t>
+          <t>His mugshot kinda looks like that forensic anthropologist&amp;#39;s rendition of Jesus Christ.</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1428,35 +1464,34 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 01:33:14</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:04:37+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>t1_ou3jg7n</t>
+          <t>t1_oy5gvw8</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>robothawk</t>
+          <t>AstronautInitial3642</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Okay but he did still have 2 years to realize that and couldve sent a shitload more.</t>
+          <t>Pretty sad downfall for someone who once spoke so much about positivity, especially with a woman and child involved.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1467,35 +1502,34 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 09:31:18</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:10:57+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>t1_ou3xn9g</t>
+          <t>t1_oy5ancw</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugm42w</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>HammerIsMyName</t>
+          <t>SubstantialPressure3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>That explains the first 2 months. After that it was clear to everyone that Russia wasn&amp;#39;t going to destroy Ukraine. Everyone was screaming at the US to stop restricting aid, incl. European aid being blocked by Biden because it contained US parts. We should remember it was the UK who finally went &amp;quot;oh shut the fuck up and do something already&amp;quot; by sending tanks to Ukraine, to show Biden that he was being a moron.</t>
+          <t>The victim told police she would not be scared if Selby returned. She told police she had video evidence but said she could not access the camera system. Christ almighty. She knew both her and her child were in danger.</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1506,35 +1540,34 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 11:23:45</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:43:51+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>t1_ou0r6ef</t>
+          <t>t1_oy5e9zo</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Prudent_Rice7840</t>
+          <t>ghidfg</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117 dogs were in various stages of decomposition Most of the recovered dogs were microchipped Investigators also located additional canine remains in another area of the field but determined they were too decomposed to justify excavation. Inside a barn on the property, investigators said they discovered an area they believe was likely used to kill dogs.  More than 600 dog collars were also recovered from that location. About 900 dogs had been sent to the rescue since January 2025. investigators allege the rescue accepted dogs and payments from shelters under agreements that the animals would be cared for and placed into homes  SO... a &amp;quot;foster dog scheme&amp;quot;?</t>
+          <t>Damn this is pretty sad. I remember watching an interview a while back where he talked about turning to hyper positivity after experiencing some pretty dark stuff.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1545,35 +1578,34 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 22:23:47</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:59:35+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>t1_ou0tk1g</t>
+          <t>t1_oy5g6ye</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DomitiusAhenobarbus_</t>
+          <t>government_not_ok</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Holy fucking shit this is awful beyond belief</t>
+          <t>Panda, panda, panda! Now making hits in the slammah.</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1584,35 +1616,34 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 22:36:29</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:07:55+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>t1_ou0wevo</t>
+          <t>t1_oy5gckd</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Humboldt-Honey</t>
+          <t>Sensitive-Memory</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>I donated really nice clothes to this rescue. Just devastated that I unknowingly supported this. Edit: Some people are confused why I would donate clothes to dogs.  This “rescue” had several thrift stores in my area to raise money. So not only were they doing this sick shit they took donations from people to sell telling them it was going to the dogs. Google Miranda’s Rescue Eureka, the website is still up.</t>
+          <t>I googled &amp;quot;panda holding hammer&amp;quot; and no shit his mug shot came up in the search results</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -1623,35 +1654,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 22:51:46</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:08:35+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>t1_ou0xm0u</t>
+          <t>t1_oy5bt1x</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz893y</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ManifestDestinysChld</t>
+          <t>Clarksp2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Ugh, I&amp;#39;m so sorry. Those monsters had so many victims. This has nothing to do with you - you did not support this! This is not something you did; this is something that was done to you. And they would&amp;#39;ve lied to and stolen from someone else if it wasn&amp;#39;t you.  You don&amp;#39;t have to waste your energy feeling bad on behalf of the evil, broken people that are responsible for this - they alone are the ones who bear the shame, not you.</t>
+          <t>I got broads in Atlanta, don’t make me come at ya wid a hamma</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -1662,35 +1692,34 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26 22:58:12</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>2026-07-17T18:48:49+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>t1_ou2qn6e</t>
+          <t>t1_oy5j1wv</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz9bsm</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_1uz9bsm</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>GodOfDarkLaughter</t>
+          <t>JadeddMillennial</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>This fucker had his finger in every pie you can think of. There is right now still a GoFundMe for them up. Here is the message on it:   Hello animal lovers and kind supporters! I’m Shannon Miranda, the founder of Miranda’s Rescue No-Kill Animal Sanctuary in Fortuna, California. This is our 31st year of rescuing and rehoming thousands of our furry friends, and our structures throughout our 38 acres are decades old.   I feel nauseated. Decades.</t>
+          <t>Targeting drinking water is an escalation if I ever saw one.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -1701,364 +1730,88 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 05:32:15</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>2026-07-17T19:20:33+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>t1_ou39bwq</t>
+          <t>t1_comment2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t3_testpost1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>t3_1ugkucg</t>
+          <t>t1_comment1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Salty_Raspberry656</t>
+          <t>commenter2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>f&amp;#39;kin sick people to be that diabolical. I hope the book is thrown at them</t>
+          <t>It was highly successful and easy to use!</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 08:03:47</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>2026-07-18T00:34:13.903775</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>t1_ifpvu1o</t>
+          <t>t1_comment1</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>t3_vwi6jx</t>
+          <t>t3_testpost1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>t3_vwi6jx</t>
+          <t>t3_testpost1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>AutoModerator</t>
+          <t>commenter1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>For homemade dishes such as lasagna, spaghetti, mac and cheese etc. please type out a basic recipe. Without this information your post will be removed after two hours. Instructions are only recommended for from scratch pasta only posts. I am a bot, and this action was performed automatically. Please contact the moderators of this subreddit if you have any questions or concerns.</t>
+          <t>What is the result of the migration?</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2022-07-11 13:16:07</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>t1_ifpybzt</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Cooking_Vito_e_Daisy</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Ytube video procedure here Recipe x 4: - 1 yellow and 1 red peppers (sorry in the TITLE I use italian name of peperoni but I mean Peppers :-) - 1 onion - basil - Olive oil - salty ricotta (or parmigiano reggiano) - pasta 400gr &amp;#x200B; Procedure description:  Cut the onion and the peppers in stripes Fry the onion in EV olive oil and after 2 min add 2/3 tablespoons of water Add the peppers, the Basil and salt, cover and cook for 10 min. &amp;#x200B;  Add some tablespoons of water if the mix becomes dry  Keep aside some stripes of peppers, for the creamy sauce blend the rest of peppers for 2-3minutes and put the sauce in the pan (turn of the heat) The pasta should be drained when it is still a little bit hard, add pasta directly in the peppers sauce Add ricotta mixing the pasta into the sauce for 2 minutes with medium heat (pay attention to the cooking time suggested by the Pasta brand). Serve it adding peppers stripes, ricotta cheese and fresh basil!!  Buon Appetito :-)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-11 13:36:13</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>t1_iftq7yl</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Giacomo_Passero</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Quanto parmigiano o ricotta?</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-12 06:10:59</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>t1_ifu6eun</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Cooking_Vito_e_Daisy</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Ciao Giacomo,  I didn&amp;#39;t report the quantity of Ricotta or Parmigiano cause in my opionion It depends on personal tastes. I think the quantity does not affect the final result. In this recipe (x 4) I grated more or less 100gr of cheese I hope it can help you, ciao ciao from Italy</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-12 09:52:45</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>t1_ifs5kza</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Grim226</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>I&amp;#39;m waiting for the rest of American to be confused</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-11 22:24:21</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>t1_ifu5sfu</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Cooking_Vito_e_Daisy</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>I&amp;#39;m waiting for the rest of American to be confused  Hello, I don&amp;#39;t understand what happened? If I can help you, ask me everything you need Ciao ciao</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-12 09:44:07</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>t1_ifu6hum</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>blisi21</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>In the USA pepperoni refers to a type of sausage, like a small salami, not the peppers.</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-12 09:53:55</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>t1_ifuu09i</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>t3_vwi6jx</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Cooking_Vito_e_Daisy</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Ops, I&amp;#39;m very sorry for this I will change immediatly my recipe Sorry and thanks for the comment</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-12 13:46:48</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>2026-07-18T00:34:13.899896</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I35"/>
+  <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2069,156 +1822,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Qa Id</t>
+          <t>Question Comment Id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Answer Comment Id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Post Id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Question Comment Id</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Answer Comment Id</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Inserted At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou3ucs8_t1_ou3tz0b</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>t3_1ugnqsp</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou3ucs8</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou3tz0b</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Why dont you mention that some of the security guards were black? Its almost like youre a race baiting moron</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>race relations  The guy kneeling on his back the entire incident was black ffs. The guardian is well known for hating Ireland and this is just another example</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou2vtr7_t1_ou3tz0b</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>t3_1ugnqsp</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou2vtr7</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou3tz0b</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>No video of a bag over his head?</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>race relations  The guy kneeling on his back the entire incident was black ffs. The guardian is well known for hating Ireland and this is just another example</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou0r6ef_t1_ou0tk1g</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>t3_1ugkucg</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou0r6ef</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>t1_ou0tk1g</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>117 dogs were in various stages of decomposition Most of the recovered dogs were microchipped Investigators also located additional canine remains in another area of the field but determined they were too decomposed to justify excavation. Inside a barn on the property, investigators said they discovered an area they believe was likely used to kill dogs.  More than 600 dog collars were also recovered from that location. About 900 dogs had been sent to the rescue since January 2025. investigators allege the rescue accepted dogs and payments from shelters under agreements that the animals would be cared for and placed into homes  SO... a &amp;quot;foster dog scheme&amp;quot;?</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Holy fucking shit this is awful beyond belief</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Score Signal</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>